--- a/results/Data/gcr_resilience_vulnerability_evidence_ledger.xlsx
+++ b/results/Data/gcr_resilience_vulnerability_evidence_ledger.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Ledger" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$I$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$I$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$158</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
   <si>
     <t>Country</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">Source(s) as cited in MS</t>
   </si>
   <si>
+    <t xml:space="preserve">Inference basis: factor source(s)</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS location</t>
   </si>
   <si>
@@ -56,7 +59,7 @@
     <t>General</t>
   </si>
   <si>
-    <t xml:space="preserve">Large industrial base with high govt influence; island; democratic; low inequality (relaxed fit)</t>
+    <t xml:space="preserve">Large industrial base with high govt influence</t>
   </si>
   <si>
     <t>resilient</t>
@@ -65,12 +68,30 @@
     <t>inference</t>
   </si>
   <si>
+    <t xml:space="preserve">Garcia Martinez et al. 2026, Boyd et al. 2023</t>
+  </si>
+  <si>
     <t>§3.1.6</t>
   </si>
   <si>
     <t xml:space="preserve">Listed under relaxed general criteria alongside NZ, UK, Iceland</t>
   </si>
   <si>
+    <t>Island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyd &amp; Wilson 2023; Baum et al. 2015</t>
+  </si>
+  <si>
+    <t>Democratic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kemp 2025, Jehn and Hoyer 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low inequality</t>
+  </si>
+  <si>
     <t>ASRS</t>
   </si>
   <si>
@@ -107,7 +128,13 @@
     <t>§3.2.4</t>
   </si>
   <si>
-    <t xml:space="preserve">large forested areas; coal/gas infrastructure</t>
+    <t xml:space="preserve">Coal/gas infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winstead &amp; Jacobson 2022; Mottaghi et al. 2023; Boyd et al. 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large forested areas</t>
   </si>
   <si>
     <t xml:space="preserve">nuclear winter</t>
@@ -128,6 +155,9 @@
     <t>vulnerable</t>
   </si>
   <si>
+    <t xml:space="preserve">General reasoning</t>
+  </si>
+  <si>
     <t xml:space="preserve">§3.2.1, §3.2.4</t>
   </si>
   <si>
@@ -137,12 +167,18 @@
     <t xml:space="preserve">No Holocene eruptions in own territory</t>
   </si>
   <si>
+    <t xml:space="preserve">Global Volcanism Program &amp; Venzke 2025 (Figure 4)</t>
+  </si>
+  <si>
     <t>NEO</t>
   </si>
   <si>
     <t xml:space="preserve">Large interior for relocation away from coastal tsunami</t>
   </si>
   <si>
+    <t xml:space="preserve">Toon et al. 1997</t>
+  </si>
+  <si>
     <t>GCIL</t>
   </si>
   <si>
@@ -161,279 +197,318 @@
     <t xml:space="preserve">AUS named among US/EU/UK/Japan/France/China</t>
   </si>
   <si>
-    <t xml:space="preserve">Good industrial base; food producer; remote; democratic; low inequality</t>
+    <t>GCBR</t>
+  </si>
+  <si>
+    <t>pandemic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Island able to enforce closed borders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyd et al. 2025a; Boyd et al. 2025b</t>
+  </si>
+  <si>
+    <t>§3.4.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Island border-control effect named</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Global Health Security Index score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron et al. 2019</t>
+  </si>
+  <si>
+    <t>§3.4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUS in highest GHS Index group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Australia limited harms over long periods (non-island jurisdiction case)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baum &amp; Adams 2023</t>
+  </si>
+  <si>
+    <t>§3.4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade dependence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Zealand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small industrial base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southern Hemisphere island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyd &amp; Wilson 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best-prospect island group with AUS, Iceland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food self-sufficient capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyd et al. 2023; Boyd &amp; Wilson 2023; Jehn et al. 2024; Mills et al. 2014; Wilson et al. 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active volcanoes in territory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Volcanism Program &amp; Venzke 2025 (Figure 4); Mani et al. 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entirely surrounded by water; tsunami exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better-resourced volcanic monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widiwijayanti et al. 2024</t>
+  </si>
+  <si>
+    <t>§3.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Located in high-likelihood space-weather damage zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maffei et al. 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§3.3.1, §3.3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NZ and Tasmania both in exposed zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High GHS Index score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson et al. 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited domestic pharmaceutical manufacturing capacity</t>
+  </si>
+  <si>
+    <t>§3.1.3</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geothermal/hydro energy independence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyd et al. 2023; Boyd &amp; Wilson 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learned volcano resilience; better-resourced monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cook &amp; Johannsdottir 2021; Islam et al. 2022</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baum et al. 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large food producer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivers et al. 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southern Hemisphere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coupe et al. 2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large food production sector; diverse crops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High inequality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical political instability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Among next-best ASRS fits for Crop Relocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blouin et al. 2025</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very democratic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food producer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low population/small industrial base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High grid inertia (hydro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bikdeli et al. 2022</t>
   </si>
   <si>
     <t>§3.3.4</t>
   </si>
   <si>
-    <t>GCBR</t>
-  </si>
-  <si>
-    <t>pandemic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island able to enforce closed borders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyd et al. 2025a; Boyd et al. 2025b</t>
-  </si>
-  <si>
-    <t>§3.4.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island border-control effect named</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Global Health Security Index score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron et al. 2019</t>
-  </si>
-  <si>
-    <t>§3.4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUS in highest GHS Index group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Western Australia limited harms over long periods (non-island jurisdiction case)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baum &amp; Adams 2023</t>
-  </si>
-  <si>
-    <t>§3.4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trade dependence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Zealand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island; democratic; low inequality (relaxed fit); small industrial base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Southern Hemisphere island; food self-sufficient capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyd &amp; Wilson 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best-prospect island group with AUS, Iceland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyd et al. 2023; Boyd &amp; Wilson 2023; Jehn et al. 2024; Mills et al. 2014; Wilson et al. 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active volcanoes in territory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entirely surrounded by water; tsunami exposure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better-resourced volcanic monitoring</t>
-  </si>
-  <si>
-    <t>§3.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Located in high-likelihood space-weather damage zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maffei et al. 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">§3.3.1, §3.3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NZ and Tasmania both in exposed zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote; democratic; low inequality; food producer; small industrial base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small industrial base limits fit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island able to enforce closed borders; exclusion/elimination strategy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High GHS Index score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trade dependence; small industrial base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limited domestic pharmaceutical manufacturing capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilson et al. 2025</t>
-  </si>
-  <si>
-    <t>§3.1.3</t>
-  </si>
-  <si>
-    <t>Iceland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island; democratic (relaxed general fit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best-prospect island group; geothermal/hydro energy independence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyd et al. 2023; Boyd &amp; Wilson 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learned volcano resilience; better-resourced monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cook &amp; Johannsdottir 2021; Islam et al. 2022</t>
-  </si>
-  <si>
-    <t>Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large food producer; (mostly) Southern Hemisphere; remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large food production sector; diverse crops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rivers et al. 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High inequality; historical political instability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Among next-best ASRS fits with Brazil, NZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blouin et al. 2025</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fits many GCIL factors if stable-democracy criterion relaxed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Among next-best ASRS fits</t>
-  </si>
-  <si>
-    <t>Uruguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very democratic; Southern Hemisphere; food producer; low population/small industrial base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Democratic; low inequality; high grid inertia (hydro); far from HEMP/geomagnetic danger</t>
+    <t xml:space="preserve">Far from HEMP/geomagnetic danger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maffei et al. 2023, General reasoning</t>
   </si>
   <si>
     <t>Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">Long Pacific coastline for seaweed; Southern Hemisphere; some climate diversity</t>
+    <t xml:space="preserve">Southern Hemisphere; some climate diversity</t>
   </si>
   <si>
     <t xml:space="preserve">Seaweed/Pacific upwelling named</t>
   </si>
   <si>
+    <t xml:space="preserve">Long Pacific coastline for seaweed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active volcanoes</t>
   </si>
   <si>
-    <t xml:space="preserve">High reliance on fisheries; high trade dependence</t>
+    <t xml:space="preserve">High trade dependence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jehn et al. 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High reliance on fisheries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scherrer et al. 2020</t>
   </si>
   <si>
     <t>Switzerland</t>
   </si>
   <si>
-    <t xml:space="preserve">Democratic; low inequality; high grid inertia (hydro); not import-dependent for power</t>
-  </si>
-  <si>
     <t>HEMP</t>
   </si>
   <si>
-    <t xml:space="preserve">Partly hardened infrastructure; possible collateral in European HEMP</t>
+    <t xml:space="preserve">Partly hardened infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">possible collateral in European HEMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong health system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuzzo &amp; Ledesma 2023; Islam et al. 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mountainous terrain aids isolation</t>
+  </si>
+  <si>
+    <t>Small/trade-dependent</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy independence (oil/hydro) supports resilience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manheim &amp; Denkenberger 2020</t>
+  </si>
+  <si>
+    <t>Scandinavia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong health systems; high GHS Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark/Finland/Norway/Sweden in highest GHS group</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very reliant on trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under nuclear umbrella - elevated targeting risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High GHS Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aged population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEMP protection efforts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pry 2017</t>
+  </si>
+  <si>
+    <t>§3.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very trade-dependent</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large industrial base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Democratic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pry 2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In high-likelihood space-weather damage zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some HEMP protection</t>
   </si>
   <si>
     <t>mixed</t>
   </si>
   <si>
-    <t xml:space="preserve">Strong health system; mountainous terrain aids isolation; small/trade-dependent</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy independence (oil/hydro) supports resilience</t>
-  </si>
-  <si>
-    <t>Scandinavia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong health systems; high GHS Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark/Finland/Norway/Sweden in highest GHS group</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large industrial base with high govt influence; island; democratic; low inequality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very reliant on trade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under nuclear umbrella - elevated targeting risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High GHS Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very trade-dependent; aged population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEMP protection efforts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pry 2017</t>
-  </si>
-  <si>
-    <t>§3.3.2</t>
-  </si>
-  <si>
-    <t>Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large industrial base; island; democratic; low inequality; very trade-dependent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island; democratic </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pry 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In high-likelihood space-weather damage zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some HEMP protection</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pry 2017; House of Commons Defence Committee 2012</t>
   </si>
   <si>
@@ -443,9 +518,6 @@
     <t>China</t>
   </si>
   <si>
-    <t xml:space="preserve">Space-weather forecasting capability; fits many GCIL factors if democracy criterion relaxed</t>
-  </si>
-  <si>
     <t xml:space="preserve">Well-organised non-island jurisdiction limiting pandemic harms</t>
   </si>
   <si>
@@ -458,22 +530,31 @@
     <t xml:space="preserve">Resilience under limited trade/reduced agricultural inputs</t>
   </si>
   <si>
+    <t xml:space="preserve">Moersdorf et al. 2023</t>
+  </si>
+  <si>
     <t>Vanuatu</t>
   </si>
   <si>
-    <t xml:space="preserve">Ample food production; high above sea level; could maintain traditional life</t>
+    <t xml:space="preserve">Ample food production</t>
   </si>
   <si>
     <t xml:space="preserve">§3.1.3, §3.2</t>
   </si>
   <si>
+    <t xml:space="preserve">High above sea level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could maintain traditional life</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lacks infrastructure/manufacturing to sustain industrial society without trade</t>
   </si>
   <si>
     <t xml:space="preserve">Solomon Islands</t>
   </si>
   <si>
-    <t xml:space="preserve">Large food excess; high above sea level</t>
+    <t xml:space="preserve">Large food excess</t>
   </si>
   <si>
     <t xml:space="preserve">Lacks infrastructure/manufacturing without trade</t>
@@ -521,18 +602,21 @@
     <t xml:space="preserve">United States</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuclear weapon state; high-latitude cooling; targeted</t>
+    <t xml:space="preserve">Nuclear weapon state</t>
   </si>
   <si>
     <t xml:space="preserve">Coupe et al. 2019; Denkenberger et al. 2017; Jehn et al. 2024; Mills et al. 2014; Scherrer et al. 2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Forecasting capability; grid hardening; high resilience spend</t>
+    <t xml:space="preserve">Forecasting capability</t>
   </si>
   <si>
     <t xml:space="preserve">Fry 2012; Johnson et al. 2016</t>
   </si>
   <si>
+    <t xml:space="preserve">Grid hardening</t>
+  </si>
+  <si>
     <t xml:space="preserve">High GHS Index but poor outcomes (political will, cohesion)</t>
   </si>
   <si>
@@ -545,10 +629,10 @@
     <t>Canada</t>
   </si>
   <si>
-    <t xml:space="preserve">High-latitude cooling; food/trade exposure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochman et al. 2022; Jehn et al. 2024; Scherrer et al. 2020</t>
+    <t xml:space="preserve">Hochman et al. 2022; Jehn et al. 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food/trade exposure</t>
   </si>
   <si>
     <t xml:space="preserve">Grid hardening against geomagnetic storms</t>
@@ -557,16 +641,13 @@
     <t xml:space="preserve">Johnson et al. 2016</t>
   </si>
   <si>
-    <t xml:space="preserve">High GHS Index; satisfies most factors except remoteness</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cameron et al. 2019; author synthesis</t>
   </si>
   <si>
     <t>Russia</t>
   </si>
   <si>
-    <t xml:space="preserve">Coupe et al. 2019; Early &amp; Asal 2014; Hochman et al. 2022; Scherrer et al. 2020</t>
+    <t xml:space="preserve">Coupe et al. 2019; Early &amp; Asal 2014; Hochman et al. 2022</t>
   </si>
   <si>
     <t>Ukraine</t>
@@ -677,9 +758,6 @@
     <t xml:space="preserve">Monsoon disruption vulnerability</t>
   </si>
   <si>
-    <t xml:space="preserve">Coupe et al. 2019</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sub-Saharan Africa</t>
   </si>
   <si>
@@ -690,6 +768,9 @@
   </si>
   <si>
     <t xml:space="preserve">Small island: sea-level rise, tsunami &amp; NEO exposure; not self-sufficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyd et al. 2023; Wilson et al. 2025)</t>
   </si>
   <si>
     <t xml:space="preserve">Marshall Islands</t>
@@ -774,7 +855,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -789,6 +870,10 @@
     </font>
     <font>
       <sz val="10.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -863,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment vertical="center" wrapText="1"/>
@@ -875,12 +960,10 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -888,6 +971,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1421,9 +1507,9 @@
     <col customWidth="1" min="4" max="4" width="59.7109375"/>
     <col customWidth="1" min="5" max="5" width="11"/>
     <col customWidth="1" min="6" max="6" width="18.7109375"/>
-    <col customWidth="1" min="7" max="7" width="34"/>
-    <col customWidth="1" min="8" max="8" width="13"/>
-    <col customWidth="1" min="9" max="9" width="38"/>
+    <col customWidth="1" min="7" max="8" width="34"/>
+    <col customWidth="1" min="9" max="9" width="13"/>
+    <col customWidth="1" min="10" max="10" width="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
@@ -1454,3279 +1540,4470 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="2"/>
+      <c r="H10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="J11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="I13" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="J13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>57</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="J14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>34</v>
+        <v>20</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="E23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>34</v>
+        <v>79</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I27" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I31" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>12</v>
+        <v>71</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>12</v>
+      <c r="E34" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>34</v>
+        <v>20</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>34</v>
+        <v>96</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38" s="2"/>
-      <c r="H38" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="2"/>
+      <c r="H38" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40" s="2"/>
-      <c r="H40" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I40" s="2"/>
+      <c r="H40" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G41" s="2"/>
-      <c r="H41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41" s="2"/>
+      <c r="H41" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G42" s="2"/>
-      <c r="H42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I42" s="2"/>
+      <c r="H42" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>106</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="J43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>34</v>
+      <c r="E44" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I44" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>34</v>
+      <c r="E45" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I45" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I47" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>12</v>
+        <v>107</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I48" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>12</v>
+        <v>108</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I49" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>119</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="J50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D51" s="2" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D52" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>34</v>
+        <v>114</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>34</v>
+        <v>115</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54" s="2"/>
-      <c r="H54" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I54" s="2"/>
+      <c r="H54" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I55" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="2"/>
       <c r="H56" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I56" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I57" s="2"/>
+      <c r="J57" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I58" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="E59" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="2"/>
       <c r="H59" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I59" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>34</v>
+        <v>128</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I60" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D61" s="2" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I61" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="2"/>
       <c r="H62" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I62" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D63" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G63" s="2"/>
-      <c r="H63" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" s="2"/>
+      <c r="H63" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>134</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="2"/>
       <c r="H64" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I64" s="2"/>
+      <c r="I64" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" s="2"/>
+      <c r="H65" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I65" s="2"/>
+      <c r="I65" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>136</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>137</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="2"/>
       <c r="H66" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I66" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>34</v>
+        <v>137</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I67" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I68" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I69" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>49</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="2"/>
       <c r="H70" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I70" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I71" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I72" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="E74" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I74" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I75" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I76" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" s="2"/>
+      <c r="H76" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>34</v>
+        <v>54</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G77" s="2"/>
-      <c r="H77" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77" s="2"/>
+      <c r="H77" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I78" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>157</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" s="2"/>
       <c r="H79" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I79" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>161</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="J80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>161</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="J81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>12</v>
+        <v>153</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I82" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>167</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" s="2"/>
       <c r="H83" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I83" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I84" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F85" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I85" s="2"/>
+      <c r="I85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>73</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" s="2"/>
       <c r="H86" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I86" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>111</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" s="2"/>
       <c r="H87" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I87" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>49</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>171</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" s="2"/>
       <c r="H88" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I88" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>34</v>
+        <v>150</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I89" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I90" s="2"/>
+      <c r="I90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>73</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" s="2"/>
       <c r="H91" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I91" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>178</v>
+        <v>54</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I92" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>34</v>
+        <v>159</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I93" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>34</v>
+        <v>160</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I94" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" s="2"/>
       <c r="H95" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I95" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I96" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I97" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="H98" s="2"/>
       <c r="I98" s="2" t="s">
-        <v>191</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>34</v>
+        <v>166</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I99" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>177</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" s="2"/>
       <c r="H100" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I100" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>34</v>
+        <v>171</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I101" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>199</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" s="2"/>
       <c r="H102" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I102" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>34</v>
+        <v>174</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I103" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>34</v>
+        <v>175</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I104" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>34</v>
+        <v>173</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I105" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>34</v>
+        <v>177</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I106" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>34</v>
+        <v>178</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I107" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>212</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" s="2"/>
       <c r="H108" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I108" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I109" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" s="2"/>
+      <c r="H109" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>34</v>
+        <v>183</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I110" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="H111" s="2"/>
       <c r="I111" s="2" t="s">
-        <v>220</v>
+        <v>28</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C112" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D112" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I112" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C113" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="D113" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>34</v>
+        <v>181</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G113" s="2"/>
-      <c r="H113" s="2" t="s">
+      <c r="H113" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I113" s="2"/>
+      <c r="I113" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C114" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I116" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" s="2"/>
+      <c r="H116" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>34</v>
+        <v>195</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I117" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>34</v>
+        <v>197</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I118" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>12</v>
+        <v>159</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I119" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I120" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>34</v>
+        <v>198</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I121" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>34</v>
+        <v>166</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I122" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J123" s="2"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J124" s="2"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J125" s="2"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H126" s="2"/>
+      <c r="I126" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J126" s="2"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J127" s="2"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J128" s="2"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J129" s="2"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J130" s="2"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J131" s="2"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J132" s="2"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J134" s="2"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J135" s="2"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J136" s="2"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J137" s="2"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J138" s="2"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J139" s="2"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J140" s="2"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J141" s="2"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J142" s="2"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J143" s="2"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D123" s="2" t="s">
+      <c r="B144" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E123" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G123" s="2" t="s">
+      <c r="E144" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H144" s="2"/>
+      <c r="I144" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J144" s="2"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H145" s="2"/>
+      <c r="I145" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J145" s="2"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H146" s="2"/>
+      <c r="I146" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147" s="2"/>
+      <c r="H147" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J147" s="2"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="2"/>
+      <c r="H148" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J148" s="2"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" s="2"/>
+      <c r="H149" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H123" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I123" s="2"/>
-    </row>
-    <row r="124" ht="14.25">
-      <c r="A124" s="2"/>
-    </row>
-    <row r="125" ht="14.25">
-      <c r="A125" s="2"/>
-    </row>
-    <row r="128" ht="14.25">
-      <c r="C128" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="D128" s="8"/>
-    </row>
-    <row r="129" ht="14.25">
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-    </row>
-    <row r="130" ht="14.25">
-      <c r="C130" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D130" s="8"/>
-    </row>
-    <row r="131" ht="14.25">
-      <c r="C131" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="132" ht="14.25">
-      <c r="C132" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="133" ht="14.25">
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-    </row>
-    <row r="134" ht="14.25">
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-    </row>
-    <row r="135" ht="14.25">
-      <c r="C135" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D135" s="8"/>
-    </row>
-    <row r="136" ht="14.25">
-      <c r="C136" s="8"/>
-      <c r="D136" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="137" ht="14.25">
-      <c r="C137" s="8"/>
-      <c r="D137" s="10" t="s">
-        <v>248</v>
+      <c r="I149" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J149" s="2"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H150" s="2"/>
+      <c r="I150" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H151" s="2"/>
+      <c r="I151" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H152" s="2"/>
+      <c r="I152" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H153" s="2"/>
+      <c r="I153" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H154" s="2"/>
+      <c r="I154" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H155" s="2"/>
+      <c r="I155" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H157" s="2"/>
+      <c r="I157" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J157" s="2"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H158" s="2"/>
+      <c r="I158" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J158" s="2"/>
+    </row>
+    <row r="159" ht="14.25">
+      <c r="A159" s="2"/>
+    </row>
+    <row r="160" ht="14.25">
+      <c r="A160" s="2"/>
+    </row>
+    <row r="163" ht="14.25">
+      <c r="C163" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D163" s="10"/>
+    </row>
+    <row r="164" ht="14.25">
+      <c r="C164" s="10"/>
+      <c r="D164" s="10"/>
+    </row>
+    <row r="165" ht="14.25">
+      <c r="C165" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D165" s="10"/>
+    </row>
+    <row r="166" ht="14.25">
+      <c r="C166" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="167" ht="14.25">
+      <c r="C167" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="168" ht="14.25">
+      <c r="C168" s="10"/>
+      <c r="D168" s="10"/>
+    </row>
+    <row r="169" ht="14.25">
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+    </row>
+    <row r="170" ht="14.25">
+      <c r="C170" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D170" s="10"/>
+    </row>
+    <row r="171" ht="14.25">
+      <c r="C171" s="10"/>
+      <c r="D171" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="172" ht="14.25">
+      <c r="C172" s="10"/>
+      <c r="D172" s="10" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I123"/>
+  <autoFilter ref="A1:J158"/>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/results/Data/gcr_resilience_vulnerability_evidence_ledger.xlsx
+++ b/results/Data/gcr_resilience_vulnerability_evidence_ledger.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Ledger" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$158</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$159</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t>Country</t>
   </si>
@@ -296,6 +296,15 @@
     <t xml:space="preserve">Wilson et al. 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Less fertilizer depedent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moersdorf et al. 2023</t>
+  </si>
+  <si>
+    <t>§3.3.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Limited domestic pharmaceutical manufacturing capacity</t>
   </si>
   <si>
@@ -377,9 +386,6 @@
     <t xml:space="preserve">Bikdeli et al. 2022</t>
   </si>
   <si>
-    <t>§3.3.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Far from HEMP/geomagnetic danger</t>
   </si>
   <si>
@@ -528,9 +534,6 @@
   </si>
   <si>
     <t xml:space="preserve">Resilience under limited trade/reduced agricultural inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moersdorf et al. 2023</t>
   </si>
   <si>
     <t>Vanuatu</t>
@@ -948,7 +951,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment vertical="center" wrapText="1"/>
@@ -960,9 +963,6 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1775,14 +1775,14 @@
         <v>34</v>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
@@ -1853,7 +1853,7 @@
       <c r="D12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -2055,7 +2055,7 @@
       <c r="D19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
@@ -2159,7 +2159,7 @@
       <c r="D23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -2275,7 +2275,7 @@
       <c r="D27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -2303,7 +2303,7 @@
       <c r="D28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2359,7 +2359,7 @@
       <c r="D30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -2445,7 +2445,7 @@
       <c r="D33" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -2473,57 +2473,59 @@
       <c r="D34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" s="2"/>
+      <c r="E34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="I34" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="J35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>13</v>
@@ -2533,7 +2535,7 @@
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>16</v>
@@ -2542,124 +2544,124 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H37" s="2"/>
+      <c r="F37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="I37" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="6" t="s">
-        <v>83</v>
-      </c>
+      <c r="F38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="J38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H39" s="2"/>
+      <c r="F39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="I39" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="J39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D40" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="6" t="s">
+      <c r="F40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="J40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>13</v>
@@ -2669,7 +2671,7 @@
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>34</v>
@@ -2678,14 +2680,14 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>13</v>
@@ -2695,7 +2697,7 @@
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>34</v>
@@ -2704,35 +2706,33 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H43" s="2"/>
+      <c r="F43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="I43" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>23</v>
@@ -2741,26 +2741,26 @@
         <v>24</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>23</v>
@@ -2769,9 +2769,9 @@
         <v>24</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E45" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>34</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>23</v>
@@ -2797,18 +2797,18 @@
         <v>24</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H46" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I46" s="2" t="s">
         <v>34</v>
       </c>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>23</v>
@@ -2825,7 +2825,7 @@
         <v>24</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>13</v>
@@ -2834,17 +2834,17 @@
         <v>26</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>23</v>
@@ -2853,26 +2853,26 @@
         <v>24</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>23</v>
@@ -2881,9 +2881,9 @@
         <v>24</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E49" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>34</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>23</v>
@@ -2909,17 +2909,17 @@
         <v>24</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>13</v>
+        <v>111</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>34</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>23</v>
@@ -2937,7 +2937,7 @@
         <v>24</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>13</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>34</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>23</v>
@@ -2965,7 +2965,7 @@
         <v>24</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>13</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>34</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>23</v>
@@ -2993,10 +2993,10 @@
         <v>24</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>43</v>
+        <v>117</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>14</v>
@@ -3012,35 +3012,35 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>13</v>
+        <v>118</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G54" s="2"/>
-      <c r="H54" s="6" t="s">
-        <v>117</v>
+      <c r="H54" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="J54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>52</v>
@@ -3058,26 +3058,26 @@
         <v>14</v>
       </c>
       <c r="G55" s="2"/>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="6" t="s">
         <v>120</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="J55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>13</v>
@@ -3087,18 +3087,16 @@
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>123</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="J56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>23</v>
@@ -3112,70 +3110,72 @@
       <c r="E57" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H57" s="2"/>
+      <c r="F57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="I57" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" s="2"/>
-      <c r="H58" s="6" t="s">
-        <v>48</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J58" s="2"/>
+      <c r="J58" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E59" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G59" s="2"/>
-      <c r="H59" s="2" t="s">
-        <v>127</v>
+      <c r="H59" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>34</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>23</v>
@@ -3195,7 +3195,7 @@
       <c r="D60" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F60" s="3" t="s">
@@ -3212,35 +3212,35 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>13</v>
+        <v>130</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="J61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>52</v>
@@ -3249,7 +3249,7 @@
         <v>24</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>13</v>
@@ -3262,13 +3262,13 @@
         <v>21</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="J62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>52</v>
@@ -3277,7 +3277,7 @@
         <v>24</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>13</v>
@@ -3286,26 +3286,26 @@
         <v>14</v>
       </c>
       <c r="G63" s="2"/>
-      <c r="H63" s="6" t="s">
-        <v>117</v>
+      <c r="H63" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="J63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>13</v>
@@ -3314,25 +3314,23 @@
         <v>14</v>
       </c>
       <c r="G64" s="2"/>
-      <c r="H64" s="2" t="s">
-        <v>44</v>
+      <c r="H64" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J64" s="6" t="s">
-        <v>133</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="J64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>134</v>
@@ -3344,17 +3342,19 @@
         <v>14</v>
       </c>
       <c r="G65" s="2"/>
-      <c r="H65" s="6" t="s">
+      <c r="H65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J65" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>58</v>
@@ -3372,8 +3372,8 @@
         <v>14</v>
       </c>
       <c r="G66" s="2"/>
-      <c r="H66" s="2" t="s">
-        <v>44</v>
+      <c r="H66" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>62</v>
@@ -3382,7 +3382,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>58</v>
@@ -3391,7 +3391,7 @@
         <v>59</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>13</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>58</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>62</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>58</v>
@@ -3447,61 +3447,63 @@
         <v>59</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J69" s="2" t="s">
-        <v>143</v>
-      </c>
+      <c r="J69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E70" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="F70" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H70" s="2"/>
       <c r="I70" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>13</v>
@@ -3511,7 +3513,7 @@
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>16</v>
@@ -3520,14 +3522,14 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>13</v>
@@ -3537,7 +3539,7 @@
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>16</v>
@@ -3546,14 +3548,14 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>13</v>
@@ -3572,24 +3574,24 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>43</v>
+        <v>22</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>16</v>
@@ -3598,18 +3600,16 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E75" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F75" s="3" t="s">
@@ -3617,53 +3617,53 @@
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>13</v>
+        <v>148</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G76" s="2"/>
-      <c r="H76" s="6" t="s">
-        <v>83</v>
+      <c r="H76" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="J76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>13</v>
@@ -3673,44 +3673,44 @@
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="6" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H78" s="2"/>
+      <c r="F78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I78" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="J78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>58</v>
@@ -3719,18 +3719,18 @@
         <v>59</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
         <v>62</v>
       </c>
@@ -3738,44 +3738,44 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H80" s="2"/>
+      <c r="E80" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I80" s="2" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="J80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>13</v>
@@ -3784,17 +3784,17 @@
         <v>26</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="J81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>58</v>
@@ -3803,18 +3803,18 @@
         <v>59</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2" t="s">
-        <v>127</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
         <v>62</v>
       </c>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>58</v>
@@ -3831,9 +3831,9 @@
         <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E83" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E83" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F83" s="3" t="s">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>62</v>
@@ -3850,40 +3850,42 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D84" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>13</v>
+        <v>150</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>13</v>
@@ -3893,7 +3895,7 @@
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>16</v>
@@ -3902,14 +3904,14 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>13</v>
@@ -3919,7 +3921,7 @@
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>16</v>
@@ -3928,14 +3930,14 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>13</v>
@@ -3954,24 +3956,24 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>43</v>
+        <v>22</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>16</v>
@@ -3980,29 +3982,27 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>131</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H89" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="I89" s="2" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="J89" s="2"/>
     </row>
@@ -4011,37 +4011,39 @@
         <v>156</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="D90" s="2" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="F90" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="J90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>13</v>
@@ -4051,7 +4053,7 @@
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>16</v>
@@ -4060,35 +4062,33 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H92" s="2"/>
+      <c r="F92" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="I92" s="2" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="J92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>52</v>
@@ -4097,16 +4097,16 @@
         <v>53</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="s">
@@ -4116,100 +4116,100 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E94" s="2" t="s">
         <v>161</v>
       </c>
+      <c r="E94" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="F94" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="J94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E95" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="F95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H95" s="2"/>
       <c r="I95" s="2" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="J95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H96" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I96" s="2" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="J96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>13</v>
@@ -4218,26 +4218,26 @@
         <v>26</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="J97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>13</v>
@@ -4246,101 +4246,101 @@
         <v>26</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="J98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2" t="s">
-        <v>105</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H99" s="2"/>
       <c r="I99" s="2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="J99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>13</v>
+      <c r="E100" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="J100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H101" s="2"/>
+      <c r="F101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="I101" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="J101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>23</v>
@@ -4349,26 +4349,26 @@
         <v>24</v>
       </c>
       <c r="D102" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="J102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>23</v>
@@ -4382,21 +4382,21 @@
       <c r="E103" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H103" s="2"/>
+      <c r="F103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="I103" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>23</v>
@@ -4407,8 +4407,8 @@
       <c r="D104" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E104" s="8" t="s">
-        <v>43</v>
+      <c r="E104" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>26</v>
@@ -4418,13 +4418,13 @@
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="J104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>23</v>
@@ -4433,26 +4433,26 @@
         <v>24</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H105" s="2"/>
       <c r="I105" s="2" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="J105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>23</v>
@@ -4461,26 +4461,26 @@
         <v>24</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H106" s="2"/>
+      <c r="F106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="I106" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>23</v>
@@ -4491,8 +4491,8 @@
       <c r="D107" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E107" s="8" t="s">
-        <v>43</v>
+      <c r="E107" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>26</v>
@@ -4502,13 +4502,13 @@
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="2" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="J107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>23</v>
@@ -4517,18 +4517,18 @@
         <v>24</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E108" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E108" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F108" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="F108" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H108" s="2"/>
       <c r="I108" s="2" t="s">
         <v>28</v>
       </c>
@@ -4536,93 +4536,91 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>13</v>
+      <c r="E109" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="2"/>
-      <c r="H109" s="6" t="s">
-        <v>83</v>
+      <c r="H109" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="J109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="E110" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F110" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H110" s="2"/>
+      <c r="F110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" s="2"/>
+      <c r="H110" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="I110" s="2" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="J110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>23</v>
@@ -4631,7 +4629,7 @@
         <v>24</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>13</v>
@@ -4640,43 +4638,45 @@
         <v>26</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="E113" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F113" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G113" s="2"/>
-      <c r="H113" s="6" t="s">
-        <v>83</v>
-      </c>
+      <c r="F113" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H113" s="2"/>
       <c r="I113" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J113" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
@@ -4686,29 +4686,29 @@
         <v>23</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H114" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114" s="2"/>
+      <c r="H114" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="I114" s="2" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="J114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>23</v>
@@ -4717,16 +4717,16 @@
         <v>38</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E115" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E115" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H115" s="2"/>
       <c r="I115" s="2" t="s">
@@ -4736,63 +4736,63 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G116" s="2"/>
-      <c r="H116" s="6" t="s">
-        <v>83</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H116" s="2"/>
       <c r="I116" s="2" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="J116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F117" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H117" s="2"/>
+      <c r="F117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G117" s="2"/>
+      <c r="H117" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="I117" s="2" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="J117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>52</v>
@@ -4801,16 +4801,16 @@
         <v>53</v>
       </c>
       <c r="D118" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="2" t="s">
@@ -4820,7 +4820,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>52</v>
@@ -4829,16 +4829,16 @@
         <v>53</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>43</v>
+        <v>198</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="2" t="s">
@@ -4848,91 +4848,91 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="2" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="J120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>43</v>
+        <v>152</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="J121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E122" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E122" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="2" t="s">
-        <v>41</v>
+        <v>201</v>
       </c>
       <c r="J122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>23</v>
@@ -4941,16 +4941,16 @@
         <v>38</v>
       </c>
       <c r="D123" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="H123" s="2"/>
       <c r="I123" s="2" t="s">
@@ -4960,35 +4960,35 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>13</v>
+      <c r="E124" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H124" s="2"/>
       <c r="I124" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>52</v>
@@ -4997,16 +4997,16 @@
         <v>53</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>43</v>
+        <v>205</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>86</v>
+        <v>206</v>
       </c>
       <c r="H125" s="2"/>
       <c r="I125" s="2" t="s">
@@ -5016,63 +5016,63 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="H126" s="2"/>
       <c r="I126" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G127" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="H127" s="2"/>
       <c r="I127" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="J127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>23</v>
@@ -5081,16 +5081,16 @@
         <v>38</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E128" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E128" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H128" s="2"/>
       <c r="I128" s="2" t="s">
@@ -5100,72 +5100,72 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E129" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E129" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="H130" s="2"/>
       <c r="I130" s="2" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="J130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>210</v>
+        <v>133</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>13</v>
@@ -5174,125 +5174,125 @@
         <v>26</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="2" t="s">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="J131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>38</v>
+        <v>211</v>
       </c>
       <c r="D132" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G132" s="2"/>
-      <c r="H132" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="J132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D133" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H133" s="2"/>
+      <c r="E133" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I133" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>218</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D134" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J134" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E134" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G134" s="2"/>
-      <c r="H134" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D135" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="H135" s="2"/>
+      <c r="E135" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I135" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J135" s="2"/>
     </row>
@@ -5301,32 +5301,32 @@
         <v>221</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>43</v>
+        <v>205</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>23</v>
@@ -5335,16 +5335,16 @@
         <v>38</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E137" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="E137" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H137" s="2"/>
       <c r="I137" s="2" t="s">
@@ -5354,7 +5354,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>23</v>
@@ -5363,16 +5363,16 @@
         <v>38</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E138" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E138" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="2" t="s">
@@ -5382,7 +5382,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>23</v>
@@ -5391,16 +5391,16 @@
         <v>38</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E139" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E139" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H139" s="2"/>
       <c r="I139" s="2" t="s">
@@ -5410,7 +5410,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>23</v>
@@ -5419,18 +5419,18 @@
         <v>38</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E140" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E140" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F140" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="F140" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H140" s="2"/>
       <c r="I140" s="2" t="s">
         <v>41</v>
       </c>
@@ -5447,18 +5447,18 @@
         <v>38</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E141" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F141" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H141" s="2"/>
+      <c r="F141" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I141" s="2" t="s">
         <v>41</v>
       </c>
@@ -5466,7 +5466,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>23</v>
@@ -5475,16 +5475,16 @@
         <v>38</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E142" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E142" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2" t="s">
@@ -5494,7 +5494,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>23</v>
@@ -5503,16 +5503,16 @@
         <v>38</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>13</v>
+        <v>234</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="2" t="s">
@@ -5522,7 +5522,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>23</v>
@@ -5531,16 +5531,16 @@
         <v>38</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>43</v>
+        <v>239</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="2" t="s">
@@ -5550,7 +5550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>23</v>
@@ -5559,16 +5559,16 @@
         <v>38</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E145" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E145" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2" t="s">
@@ -5578,72 +5578,74 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D146" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>13</v>
+      <c r="E146" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>217</v>
+        <v>108</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J146" s="2" t="s">
-        <v>246</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H147" s="2"/>
+      <c r="I147" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J147" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G147" s="2"/>
-      <c r="H147" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E148" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E148" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F148" s="3" t="s">
@@ -5651,44 +5653,42 @@
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>13</v>
+        <v>249</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="6" t="s">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>52</v>
@@ -5697,18 +5697,18 @@
         <v>53</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H150" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" s="2"/>
+      <c r="H150" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I150" s="2" t="s">
         <v>87</v>
       </c>
@@ -5725,9 +5725,9 @@
         <v>53</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E151" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E151" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F151" s="4" t="s">
@@ -5744,7 +5744,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>52</v>
@@ -5753,9 +5753,9 @@
         <v>53</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E152" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E152" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F152" s="4" t="s">
@@ -5772,7 +5772,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>52</v>
@@ -5781,9 +5781,9 @@
         <v>53</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E153" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E153" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F153" s="4" t="s">
@@ -5800,44 +5800,44 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>255</v>
+        <v>143</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>257</v>
+        <v>86</v>
       </c>
       <c r="H154" s="2"/>
       <c r="I154" s="2" t="s">
-        <v>258</v>
+        <v>87</v>
       </c>
       <c r="J154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>13</v>
@@ -5846,17 +5846,17 @@
         <v>26</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="2" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="J155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>58</v>
@@ -5865,26 +5865,26 @@
         <v>59</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>43</v>
+        <v>261</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="2" t="s">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="J156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>58</v>
@@ -5893,26 +5893,26 @@
         <v>59</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E157" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E157" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>65</v>
+        <v>265</v>
       </c>
       <c r="H157" s="2"/>
       <c r="I157" s="2" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="J157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>58</v>
@@ -5921,9 +5921,9 @@
         <v>59</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E158" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E158" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F158" s="4" t="s">
@@ -5938,72 +5938,100 @@
       </c>
       <c r="J158" s="2"/>
     </row>
-    <row r="159" ht="14.25">
-      <c r="A159" s="2"/>
+    <row r="159">
+      <c r="A159" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H159" s="2"/>
+      <c r="I159" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J159" s="2"/>
     </row>
     <row r="160" ht="14.25">
       <c r="A160" s="2"/>
     </row>
-    <row r="163" ht="14.25">
-      <c r="C163" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D163" s="10"/>
+    <row r="161" ht="14.25">
+      <c r="A161" s="2"/>
     </row>
     <row r="164" ht="14.25">
-      <c r="C164" s="10"/>
-      <c r="D164" s="10"/>
+      <c r="C164" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D164" s="9"/>
     </row>
     <row r="165" ht="14.25">
-      <c r="C165" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="D165" s="10"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
     </row>
     <row r="166" ht="14.25">
       <c r="C166" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D166" s="10" t="s">
         <v>271</v>
       </c>
+      <c r="D166" s="9"/>
     </row>
     <row r="167" ht="14.25">
-      <c r="C167" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D167" s="10" t="s">
+      <c r="C167" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D167" s="9" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="168" ht="14.25">
-      <c r="C168" s="10"/>
-      <c r="D168" s="10"/>
+      <c r="C168" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="169" ht="14.25">
-      <c r="C169" s="10"/>
-      <c r="D169" s="10"/>
+      <c r="C169" s="9"/>
+      <c r="D169" s="9"/>
     </row>
     <row r="170" ht="14.25">
-      <c r="C170" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="D170" s="10"/>
+      <c r="C170" s="9"/>
+      <c r="D170" s="9"/>
     </row>
     <row r="171" ht="14.25">
-      <c r="C171" s="10"/>
-      <c r="D171" s="10" t="s">
+      <c r="C171" s="11" t="s">
         <v>274</v>
       </c>
+      <c r="D171" s="9"/>
     </row>
     <row r="172" ht="14.25">
-      <c r="C172" s="10"/>
-      <c r="D172" s="10" t="s">
+      <c r="C172" s="9"/>
+      <c r="D172" s="9" t="s">
         <v>275</v>
       </c>
     </row>
+    <row r="173" ht="14.25">
+      <c r="C173" s="9"/>
+      <c r="D173" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J158"/>
+  <autoFilter ref="A1:J159"/>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/results/Data/gcr_resilience_vulnerability_evidence_ledger.xlsx
+++ b/results/Data/gcr_resilience_vulnerability_evidence_ledger.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Ledger" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$J$158</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
@@ -452,343 +452,343 @@
     <t xml:space="preserve">Manheim &amp; Denkenberger 2020</t>
   </si>
   <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong health systems; high GHS Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark/Finland/Norway/Sweden in highest GHS group</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very reliant on trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under nuclear umbrella - elevated targeting risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High GHS Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aged population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEMP protection efforts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pry 2017</t>
+  </si>
+  <si>
+    <t>§3.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very trade-dependent</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Democratic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pry 2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In high-likelihood space-weather damage zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some HEMP protection</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pry 2017; House of Commons Defence Committee 2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclear weapon state / NATO - elevated direct-targeting risk</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well-organised non-island jurisdiction limiting pandemic harms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-latitude cooling</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resilience under limited trade/reduced agricultural inputs</t>
+  </si>
+  <si>
+    <t>Vanuatu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ample food production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§3.1.3, §3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High above sea level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could maintain traditional life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lacks infrastructure/manufacturing to sustain industrial society without trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solomon Islands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large food excess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lacks infrastructure/manufacturing without trade</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk from social/political instability during ASRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learned volcano resilience</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resilient location for climate/food impacts (equatorial upwelling, seaweed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jehn et al. 2024; Scherrer et al. 2020</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equatorial Andes - prime food stockpile siting (La Paz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maher &amp; Baum 2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stockpile location, not population resilience per se</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equatorial Andes - prime food stockpile siting (Pasto)</t>
+  </si>
+  <si>
+    <t>Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclear weapon state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coupe et al. 2019; Denkenberger et al. 2017; Jehn et al. 2024; Mills et al. 2014; Scherrer et al. 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecasting capability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fry 2012; Johnson et al. 2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid hardening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High GHS Index but poor outcomes (political will, cohesion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyu et al. 2023; Nuzzo &amp; Ledesma 2023</t>
+  </si>
+  <si>
+    <t>§3.4.3</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochman et al. 2022; Jehn et al. 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food/trade exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid hardening against geomagnetic storms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson et al. 2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron et al. 2019; author synthesis</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coupe et al. 2019; Early &amp; Asal 2014; Hochman et al. 2022</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>cyber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverted grid to manual control after cyberattack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knake 2017</t>
+  </si>
+  <si>
+    <t>§3.3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At risk from Russia - elevated direct-targeting risk</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fared reasonably well as climate refuge after Toba supereruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black et al. 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep-time analogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclear weapon state - elevated direct-targeting risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named in nuclear-winter at-risk list; nuclear weapon state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochman et al. 2022</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named in nuclear-winter at-risk list; nuclear weapon state / conflict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early &amp; Asal 2014</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named in at-risk list; conflict with Israel/US - targeting risk</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named in at-risk list; nuclear weapon state</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High cooling / agricultural exposure in nuclear winter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jehn et al. 2024, 2025a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coupe et al. 2019; Jehn et al. 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southern Africa &amp; South America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparatively resilient to climate/food impacts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mills et al. 2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediterranean climate zones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Climate-zone vulnerability in nuclear winter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grime 1986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asian monsoon regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsoon disruption vulnerability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep-time analogue; paired with India in text</t>
+  </si>
+  <si>
+    <t>Tuvalu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small island: sea-level rise, tsunami &amp; NEO exposure; not self-sufficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyd et al. 2023; Wilson et al. 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marshall Islands</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Germany in high-likelihood space-weather damage zone</t>
+  </si>
+  <si>
+    <t>Baltics</t>
+  </si>
+  <si>
     <t>Scandinavia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong health systems; high GHS Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark/Finland/Norway/Sweden in highest GHS group</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very reliant on trade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under nuclear umbrella - elevated targeting risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High GHS Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aged population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEMP protection efforts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pry 2017</t>
-  </si>
-  <si>
-    <t>§3.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very trade-dependent</t>
-  </si>
-  <si>
-    <t>Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large industrial base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Democratic </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pry 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In high-likelihood space-weather damage zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some HEMP protection</t>
-  </si>
-  <si>
-    <t>mixed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pry 2017; House of Commons Defence Committee 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuclear weapon state / NATO - elevated direct-targeting risk</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well-organised non-island jurisdiction limiting pandemic harms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High-latitude cooling</t>
-  </si>
-  <si>
-    <t>Cuba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resilience under limited trade/reduced agricultural inputs</t>
-  </si>
-  <si>
-    <t>Vanuatu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ample food production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">§3.1.3, §3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High above sea level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could maintain traditional life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lacks infrastructure/manufacturing to sustain industrial society without trade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solomon Islands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large food excess</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lacks infrastructure/manufacturing without trade</t>
-  </si>
-  <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk from social/political instability during ASRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learned volcano resilience</t>
-  </si>
-  <si>
-    <t>Peru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resilient location for climate/food impacts (equatorial upwelling, seaweed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jehn et al. 2024; Scherrer et al. 2020</t>
-  </si>
-  <si>
-    <t>Bolivia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equatorial Andes - prime food stockpile siting (La Paz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maher &amp; Baum 2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stockpile location, not population resilience per se</t>
-  </si>
-  <si>
-    <t>Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equatorial Andes - prime food stockpile siting (Pasto)</t>
-  </si>
-  <si>
-    <t>Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuclear weapon state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coupe et al. 2019; Denkenberger et al. 2017; Jehn et al. 2024; Mills et al. 2014; Scherrer et al. 2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecasting capability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fry 2012; Johnson et al. 2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid hardening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High GHS Index but poor outcomes (political will, cohesion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyu et al. 2023; Nuzzo &amp; Ledesma 2023</t>
-  </si>
-  <si>
-    <t>§3.4.3</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochman et al. 2022; Jehn et al. 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food/trade exposure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid hardening against geomagnetic storms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johnson et al. 2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron et al. 2019; author synthesis</t>
-  </si>
-  <si>
-    <t>Russia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coupe et al. 2019; Early &amp; Asal 2014; Hochman et al. 2022</t>
-  </si>
-  <si>
-    <t>Ukraine</t>
-  </si>
-  <si>
-    <t>cyber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverted grid to manual control after cyberattack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knake 2017</t>
-  </si>
-  <si>
-    <t>§3.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At risk from Russia - elevated direct-targeting risk</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fared reasonably well as climate refuge after Toba supereruption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black et al. 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep-time analogue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuclear weapon state - elevated direct-targeting risk</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Named in nuclear-winter at-risk list; nuclear weapon state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochman et al. 2022</t>
-  </si>
-  <si>
-    <t>Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Named in nuclear-winter at-risk list; nuclear weapon state / conflict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Early &amp; Asal 2014</t>
-  </si>
-  <si>
-    <t>Iran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Named in at-risk list; conflict with Israel/US - targeting risk</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Named in at-risk list; nuclear weapon state</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High cooling / agricultural exposure in nuclear winter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jehn et al. 2024, 2025a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coupe et al. 2019; Jehn et al. 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Southern Africa &amp; South America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparatively resilient to climate/food impacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mills et al. 2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mediterranean climate zones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Climate-zone vulnerability in nuclear winter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grime 1986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asian monsoon regions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monsoon disruption vulnerability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sub-Saharan Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep-time analogue; paired with India in text</t>
-  </si>
-  <si>
-    <t>Tuvalu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small island: sea-level rise, tsunami &amp; NEO exposure; not self-sufficient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyd et al. 2023; Wilson et al. 2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marshall Islands</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern Germany in high-likelihood space-weather damage zone</t>
-  </si>
-  <si>
-    <t>Baltics</t>
   </si>
   <si>
     <t xml:space="preserve">European Union</t>
@@ -872,16 +872,16 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="11.000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="11.000000"/>
+      <color rgb="FF9A1B1B"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.000000"/>
-      <color rgb="FF9A1B1B"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1768,7 +1768,7 @@
         <v>14</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -1804,7 +1804,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -1853,7 +1853,7 @@
       <c r="D12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -1888,7 +1888,7 @@
         <v>14</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="2" t="s">
         <v>48</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -2055,7 +2055,7 @@
       <c r="D19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
@@ -2159,7 +2159,7 @@
       <c r="D23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -2275,7 +2275,7 @@
       <c r="D27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -2303,7 +2303,7 @@
       <c r="D28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2338,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="G29" s="2"/>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I29" s="2" t="s">
@@ -2359,7 +2359,7 @@
       <c r="D30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -2445,7 +2445,7 @@
       <c r="D33" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -2473,7 +2473,7 @@
       <c r="D34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -2501,7 +2501,7 @@
       <c r="D35" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F35" s="4" t="s">
@@ -2616,7 +2616,7 @@
         <v>14</v>
       </c>
       <c r="G39" s="2"/>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2670,7 +2670,7 @@
         <v>14</v>
       </c>
       <c r="G41" s="2"/>
-      <c r="H41" s="6" t="s">
+      <c r="H41" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I41" s="2" t="s">
@@ -2696,7 +2696,7 @@
         <v>14</v>
       </c>
       <c r="G42" s="2"/>
-      <c r="H42" s="6" t="s">
+      <c r="H42" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I42" s="2" t="s">
@@ -2722,7 +2722,7 @@
         <v>14</v>
       </c>
       <c r="G43" s="2"/>
-      <c r="H43" s="6" t="s">
+      <c r="H43" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I43" s="2" t="s">
@@ -2771,7 +2771,7 @@
       <c r="D45" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -2799,7 +2799,7 @@
       <c r="D46" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -2883,7 +2883,7 @@
       <c r="D49" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -2911,7 +2911,7 @@
       <c r="D50" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -2931,11 +2931,9 @@
         <v>115</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
         <v>116</v>
       </c>
@@ -3015,15 +3013,13 @@
         <v>115</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F54" s="3" t="s">
@@ -3058,7 +3054,7 @@
         <v>14</v>
       </c>
       <c r="G55" s="2"/>
-      <c r="H55" s="6" t="s">
+      <c r="H55" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I55" s="2" t="s">
@@ -3167,14 +3163,14 @@
       <c r="D59" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G59" s="2"/>
-      <c r="H59" s="6" t="s">
+      <c r="H59" s="2" t="s">
         <v>48</v>
       </c>
       <c r="I59" s="2" t="s">
@@ -3195,7 +3191,7 @@
       <c r="D60" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F60" s="3" t="s">
@@ -3223,7 +3219,7 @@
       <c r="D61" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F61" s="3" t="s">
@@ -3314,7 +3310,7 @@
         <v>14</v>
       </c>
       <c r="G64" s="2"/>
-      <c r="H64" s="6" t="s">
+      <c r="H64" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I64" s="2" t="s">
@@ -3348,7 +3344,7 @@
       <c r="I65" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J65" s="6" t="s">
+      <c r="J65" s="2" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3372,7 +3368,7 @@
         <v>14</v>
       </c>
       <c r="G66" s="2"/>
-      <c r="H66" s="6" t="s">
+      <c r="H66" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I66" s="2" t="s">
@@ -3441,13 +3437,11 @@
         <v>140</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>13</v>
@@ -3457,79 +3451,79 @@
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="J69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H70" s="2"/>
+      <c r="F70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="I70" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>145</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D71" s="2" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="F71" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H71" s="2"/>
       <c r="I71" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D72" s="2" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>13</v>
@@ -3539,85 +3533,93 @@
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D73" s="2" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="F73" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D74" s="2" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="F74" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>16</v>
@@ -3626,44 +3628,40 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>13</v>
@@ -3672,26 +3670,24 @@
         <v>14</v>
       </c>
       <c r="G77" s="2"/>
-      <c r="H77" s="6" t="s">
-        <v>83</v>
+      <c r="H77" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="J77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>13</v>
@@ -3700,56 +3696,54 @@
         <v>14</v>
       </c>
       <c r="G78" s="2"/>
-      <c r="H78" s="6" t="s">
-        <v>55</v>
+      <c r="H78" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="J78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H79" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="I79" s="2" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="J79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E80" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E80" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F80" s="3" t="s">
@@ -3760,69 +3754,69 @@
         <v>44</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H81" s="2"/>
+      <c r="F81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="I81" s="2" t="s">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="J81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H82" s="2"/>
+      <c r="F82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="I82" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="J82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>58</v>
@@ -3831,18 +3825,18 @@
         <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2" t="s">
-        <v>129</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
         <v>62</v>
       </c>
@@ -3850,7 +3844,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>58</v>
@@ -3859,9 +3853,9 @@
         <v>59</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E84" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F84" s="3" t="s">
@@ -3878,159 +3872,167 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="D85" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="F85" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="J85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D86" s="2" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="F86" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>13</v>
+      <c r="E87" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D88" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>13</v>
+        <v>151</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="D89" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="J89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H90" s="2"/>
+      <c r="F90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="I90" s="2" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="J90" s="2"/>
     </row>
@@ -4043,7 +4045,7 @@
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>13</v>
@@ -4053,7 +4055,7 @@
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>16</v>
@@ -4065,24 +4067,26 @@
         <v>158</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="D92" s="2" t="s">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="F92" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J92" s="2"/>
     </row>
@@ -4097,16 +4101,16 @@
         <v>53</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="s">
@@ -4122,23 +4126,23 @@
         <v>52</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>43</v>
+        <v>162</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="J94" s="2"/>
     </row>
@@ -4147,54 +4151,54 @@
         <v>158</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H95" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I95" s="2" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="J95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="J96" s="2"/>
     </row>
@@ -4206,10 +4210,10 @@
         <v>52</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>13</v>
@@ -4218,11 +4222,11 @@
         <v>26</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="J97" s="2"/>
     </row>
@@ -4231,13 +4235,13 @@
         <v>166</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>13</v>
@@ -4246,11 +4250,11 @@
         <v>26</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2" t="s">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="J98" s="2"/>
     </row>
@@ -4259,82 +4263,82 @@
         <v>166</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H99" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="I99" s="2" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="J99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>43</v>
+        <v>170</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="J100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="F101" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H101" s="2"/>
       <c r="I101" s="2" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="J101" s="2"/>
     </row>
@@ -4349,18 +4353,18 @@
         <v>24</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H102" s="2"/>
+      <c r="F102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="I102" s="2" t="s">
         <v>173</v>
       </c>
@@ -4377,18 +4381,18 @@
         <v>24</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F103" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="F103" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H103" s="2"/>
       <c r="I103" s="2" t="s">
         <v>173</v>
       </c>
@@ -4405,10 +4409,10 @@
         <v>24</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>13</v>
+        <v>176</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>26</v>
@@ -4418,13 +4422,13 @@
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2" t="s">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="J104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>23</v>
@@ -4433,20 +4437,20 @@
         <v>24</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H105" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="I105" s="2" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="J105" s="2"/>
     </row>
@@ -4461,18 +4465,18 @@
         <v>24</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="F106" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H106" s="2"/>
       <c r="I106" s="2" t="s">
         <v>173</v>
       </c>
@@ -4489,10 +4493,10 @@
         <v>24</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>13</v>
+        <v>179</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>26</v>
@@ -4502,13 +4506,13 @@
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="2" t="s">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="J107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>23</v>
@@ -4517,18 +4521,18 @@
         <v>24</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E108" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E108" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F108" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H108" s="2"/>
+      <c r="F108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I108" s="2" t="s">
         <v>28</v>
       </c>
@@ -4542,66 +4546,66 @@
         <v>23</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>43</v>
+        <v>182</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="J109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F110" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G110" s="2"/>
-      <c r="H110" s="6" t="s">
-        <v>83</v>
-      </c>
+      <c r="F110" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H110" s="2"/>
       <c r="I110" s="2" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="J110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>13</v>
@@ -4610,17 +4614,19 @@
         <v>26</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J111" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>23</v>
@@ -4629,7 +4635,7 @@
         <v>24</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>13</v>
@@ -4650,59 +4656,57 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F113" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H113" s="2"/>
+      <c r="F113" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="I113" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="J113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G114" s="2"/>
-      <c r="H114" s="6" t="s">
-        <v>83</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H114" s="2"/>
       <c r="I114" s="2" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="J114" s="2"/>
     </row>
@@ -4717,9 +4721,9 @@
         <v>38</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E115" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E115" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F115" s="4" t="s">
@@ -4742,23 +4746,23 @@
         <v>23</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H116" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="I116" s="2" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="J116" s="2"/>
     </row>
@@ -4767,26 +4771,26 @@
         <v>193</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F117" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G117" s="2"/>
-      <c r="H117" s="6" t="s">
-        <v>83</v>
-      </c>
+      <c r="F117" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H117" s="2"/>
       <c r="I117" s="2" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="J117" s="2"/>
     </row>
@@ -4801,7 +4805,7 @@
         <v>53</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>13</v>
@@ -4829,16 +4833,16 @@
         <v>53</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>197</v>
+        <v>86</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="2" t="s">
@@ -4854,23 +4858,23 @@
         <v>52</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>43</v>
+        <v>153</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="2" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="J120" s="2"/>
     </row>
@@ -4879,54 +4883,54 @@
         <v>193</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>13</v>
+        <v>199</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="2" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="J121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E122" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E122" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="2" t="s">
-        <v>201</v>
+        <v>41</v>
       </c>
       <c r="J122" s="2"/>
     </row>
@@ -4941,9 +4945,9 @@
         <v>38</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E123" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E123" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F123" s="4" t="s">
@@ -4963,26 +4967,26 @@
         <v>202</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>43</v>
+        <v>205</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H124" s="2"/>
       <c r="I124" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J124" s="2"/>
     </row>
@@ -4997,16 +5001,16 @@
         <v>53</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="H125" s="2"/>
       <c r="I125" s="2" t="s">
@@ -5019,54 +5023,54 @@
         <v>202</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>43</v>
+        <v>150</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>86</v>
+        <v>207</v>
       </c>
       <c r="H126" s="2"/>
       <c r="I126" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>13</v>
+        <v>194</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H127" s="2"/>
       <c r="I127" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J127" s="2"/>
     </row>
@@ -5081,9 +5085,9 @@
         <v>38</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E128" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E128" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F128" s="4" t="s">
@@ -5103,26 +5107,26 @@
         <v>208</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E129" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E129" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>209</v>
+        <v>86</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J129" s="2"/>
     </row>
@@ -5134,38 +5138,38 @@
         <v>52</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>43</v>
+        <v>153</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="H130" s="2"/>
       <c r="I130" s="2" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="J130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>133</v>
+        <v>211</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>13</v>
@@ -5174,11 +5178,11 @@
         <v>26</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="2" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="J131" s="2"/>
     </row>
@@ -5187,56 +5191,58 @@
         <v>210</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>211</v>
+        <v>38</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H132" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I132" s="2" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
       <c r="J132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F133" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H133" s="2"/>
       <c r="I133" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J133" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
@@ -5246,53 +5252,51 @@
         <v>23</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H134" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I134" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>219</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H135" s="2"/>
       <c r="I135" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J135" s="2"/>
     </row>
@@ -5301,32 +5305,32 @@
         <v>221</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>13</v>
+        <v>222</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>23</v>
@@ -5335,16 +5339,16 @@
         <v>38</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E137" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E137" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H137" s="2"/>
       <c r="I137" s="2" t="s">
@@ -5354,7 +5358,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>23</v>
@@ -5363,16 +5367,16 @@
         <v>38</v>
       </c>
       <c r="D138" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G138" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="2" t="s">
@@ -5382,7 +5386,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>23</v>
@@ -5391,16 +5395,16 @@
         <v>38</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E139" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E139" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H139" s="2"/>
       <c r="I139" s="2" t="s">
@@ -5410,7 +5414,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>23</v>
@@ -5419,18 +5423,18 @@
         <v>38</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E140" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E140" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F140" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H140" s="2"/>
+      <c r="F140" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I140" s="2" t="s">
         <v>41</v>
       </c>
@@ -5447,18 +5451,18 @@
         <v>38</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E141" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E141" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F141" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G141" s="2"/>
-      <c r="H141" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="F141" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H141" s="2"/>
       <c r="I141" s="2" t="s">
         <v>41</v>
       </c>
@@ -5466,7 +5470,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>23</v>
@@ -5475,16 +5479,16 @@
         <v>38</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E142" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E142" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2" t="s">
@@ -5494,7 +5498,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>23</v>
@@ -5503,16 +5507,16 @@
         <v>38</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>43</v>
+        <v>238</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="2" t="s">
@@ -5522,7 +5526,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>23</v>
@@ -5531,16 +5535,16 @@
         <v>38</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>13</v>
+        <v>241</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="2" t="s">
@@ -5550,7 +5554,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>23</v>
@@ -5559,16 +5563,16 @@
         <v>38</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E145" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E145" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>243</v>
+        <v>108</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2" t="s">
@@ -5578,82 +5582,80 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E146" s="7" t="s">
-        <v>43</v>
+        <v>217</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J146" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H147" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="I147" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>247</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="J147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F148" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G148" s="2"/>
-      <c r="H148" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>95</v>
@@ -5662,33 +5664,35 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C149" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="D149" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E149" s="7" t="s">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G149" s="2"/>
-      <c r="H149" s="6" t="s">
-        <v>250</v>
+      <c r="H149" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>52</v>
@@ -5697,18 +5701,18 @@
         <v>53</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" s="2"/>
-      <c r="H150" s="6" t="s">
-        <v>55</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H150" s="2"/>
       <c r="I150" s="2" t="s">
         <v>87</v>
       </c>
@@ -5725,9 +5729,9 @@
         <v>53</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E151" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E151" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F151" s="4" t="s">
@@ -5744,7 +5748,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>52</v>
@@ -5753,9 +5757,9 @@
         <v>53</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E152" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E152" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F152" s="4" t="s">
@@ -5783,7 +5787,7 @@
       <c r="D153" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E153" s="7" t="s">
+      <c r="E153" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F153" s="4" t="s">
@@ -5800,44 +5804,44 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>43</v>
+        <v>257</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>86</v>
+        <v>258</v>
       </c>
       <c r="H154" s="2"/>
       <c r="I154" s="2" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
       <c r="J154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>13</v>
@@ -5846,17 +5850,17 @@
         <v>26</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="2" t="s">
-        <v>259</v>
+        <v>70</v>
       </c>
       <c r="J155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>58</v>
@@ -5865,26 +5869,26 @@
         <v>59</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>13</v>
+        <v>264</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="2" t="s">
-        <v>70</v>
+        <v>201</v>
       </c>
       <c r="J156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>58</v>
@@ -5893,26 +5897,26 @@
         <v>59</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E157" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E157" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>265</v>
+        <v>65</v>
       </c>
       <c r="H157" s="2"/>
       <c r="I157" s="2" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="J157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>58</v>
@@ -5921,9 +5925,9 @@
         <v>59</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E158" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E158" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F158" s="4" t="s">
@@ -5938,100 +5942,72 @@
       </c>
       <c r="J158" s="2"/>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E159" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H159" s="2"/>
-      <c r="I159" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J159" s="2"/>
+    <row r="159" ht="14.25">
+      <c r="A159" s="7"/>
     </row>
     <row r="160" ht="14.25">
-      <c r="A160" s="2"/>
-    </row>
-    <row r="161" ht="14.25">
-      <c r="A161" s="2"/>
+      <c r="A160" s="7"/>
+    </row>
+    <row r="163" ht="14.25">
+      <c r="C163" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D163" s="9"/>
     </row>
     <row r="164" ht="14.25">
-      <c r="C164" s="8" t="s">
-        <v>270</v>
-      </c>
+      <c r="C164" s="9"/>
       <c r="D164" s="9"/>
     </row>
     <row r="165" ht="14.25">
-      <c r="C165" s="9"/>
+      <c r="C165" s="10" t="s">
+        <v>271</v>
+      </c>
       <c r="D165" s="9"/>
     </row>
     <row r="166" ht="14.25">
-      <c r="C166" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="D166" s="9"/>
+      <c r="C166" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="167" ht="14.25">
       <c r="C167" s="9" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="168" ht="14.25">
-      <c r="C168" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D168" s="9" t="s">
-        <v>273</v>
-      </c>
+      <c r="C168" s="9"/>
+      <c r="D168" s="9"/>
     </row>
     <row r="169" ht="14.25">
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
     </row>
     <row r="170" ht="14.25">
-      <c r="C170" s="9"/>
+      <c r="C170" s="11" t="s">
+        <v>274</v>
+      </c>
       <c r="D170" s="9"/>
     </row>
     <row r="171" ht="14.25">
-      <c r="C171" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D171" s="9"/>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="172" ht="14.25">
       <c r="C172" s="9"/>
       <c r="D172" s="9" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="173" ht="14.25">
-      <c r="C173" s="9"/>
-      <c r="D173" s="9" t="s">
         <v>276</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J159"/>
+  <autoFilter ref="A1:J158"/>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
